--- a/artfynd/A 28842-2022 artfynd.xlsx
+++ b/artfynd/A 28842-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28842-2022 artfynd.xlsx
+++ b/artfynd/A 28842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>73695379</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450232.9823899046</v>
+        <v>450233</v>
       </c>
       <c r="R2" t="n">
-        <v>6436307.784923892</v>
+        <v>6436308</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +753,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,42 +787,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73695378</v>
+        <v>73695380</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450224.012180966</v>
+        <v>450175</v>
       </c>
       <c r="R3" t="n">
-        <v>6436311.071478983</v>
+        <v>6436316</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +865,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,19 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73695380</v>
+        <v>73695382</v>
       </c>
       <c r="B4" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -964,7 +929,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450174.7758517757</v>
+        <v>449943</v>
       </c>
       <c r="R4" t="n">
-        <v>6436315.919704827</v>
+        <v>6436201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,19 +977,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,16 +1014,11 @@
         <v>79762823</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1097,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450185.9718331654</v>
+        <v>450186</v>
       </c>
       <c r="R5" t="n">
-        <v>6436321.070430785</v>
+        <v>6436321</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1168,6 +1118,230 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73695381</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5A, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>449958</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6436214</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>73695378</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5A, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450224</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6436311</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 28842-2022 artfynd.xlsx
+++ b/artfynd/A 28842-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695380</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79762823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695381</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,8 +1374,21 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>